--- a/faculty_data.xlsx
+++ b/faculty_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drlak\my_projects\projects_myTimetable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1641C0AF-0C29-42C7-AEF7-822868A20531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C733D3-0CD2-422E-B4E6-250AF9470A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="990" yWindow="5100" windowWidth="17925" windowHeight="10305" xr2:uid="{133CB0F7-179D-4473-A91B-779EACBBF9B7}"/>
+    <workbookView xWindow="16890" yWindow="2040" windowWidth="11310" windowHeight="9420" activeTab="2" xr2:uid="{133CB0F7-179D-4473-A91B-779EACBBF9B7}"/>
   </bookViews>
   <sheets>
     <sheet name="CE" sheetId="1" r:id="rId1"/>
@@ -36,31 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="38">
-  <si>
-    <t>Rosa</t>
-  </si>
-  <si>
-    <t>Zvl</t>
-  </si>
-  <si>
-    <t>Elviz</t>
-  </si>
-  <si>
-    <t>Nivi</t>
-  </si>
-  <si>
-    <t>Chino</t>
-  </si>
-  <si>
-    <t>Anjana</t>
-  </si>
-  <si>
-    <t>Ezri</t>
-  </si>
-  <si>
-    <t>Ezer</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="47">
   <si>
     <t>AP1</t>
   </si>
@@ -86,9 +62,6 @@
     <t>AP5</t>
   </si>
   <si>
-    <t>Zadie</t>
-  </si>
-  <si>
     <t>AP6</t>
   </si>
   <si>
@@ -116,15 +89,9 @@
     <t>dept</t>
   </si>
   <si>
-    <t>faculty_name</t>
-  </si>
-  <si>
     <t>nick_name</t>
   </si>
   <si>
-    <t>position</t>
-  </si>
-  <si>
     <t>ROSA</t>
   </si>
   <si>
@@ -150,6 +117,66 @@
   </si>
   <si>
     <t>ZADIE</t>
+  </si>
+  <si>
+    <t>BINU</t>
+  </si>
+  <si>
+    <t>ELDOSE</t>
+  </si>
+  <si>
+    <t>JOHN</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>ABIN</t>
+  </si>
+  <si>
+    <t>MANOJ</t>
+  </si>
+  <si>
+    <t>SURESH</t>
+  </si>
+  <si>
+    <t>BABU</t>
+  </si>
+  <si>
+    <t>JACOB</t>
+  </si>
+  <si>
+    <t>RENJI</t>
+  </si>
+  <si>
+    <t>CHACKO</t>
+  </si>
+  <si>
+    <t>ABY</t>
+  </si>
+  <si>
+    <t>JAYAN</t>
+  </si>
+  <si>
+    <t>SIJU</t>
+  </si>
+  <si>
+    <t>JINS</t>
+  </si>
+  <si>
+    <t>MANI</t>
+  </si>
+  <si>
+    <t>LUCY</t>
+  </si>
+  <si>
+    <t>JESSY</t>
+  </si>
+  <si>
+    <t>grade</t>
+  </si>
+  <si>
+    <t>py_band</t>
   </si>
 </sst>
 </file>
@@ -520,19 +547,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -540,16 +567,16 @@
         <v>1001</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -557,16 +584,16 @@
         <v>1002</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -574,16 +601,16 @@
         <v>1003</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -591,16 +618,16 @@
         <v>1004</v>
       </c>
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -608,16 +635,16 @@
         <v>1005</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -625,16 +652,16 @@
         <v>1006</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -642,16 +669,16 @@
         <v>1007</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -659,16 +686,16 @@
         <v>1008</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -676,16 +703,16 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -709,19 +736,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -729,16 +756,16 @@
         <v>2001</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -746,16 +773,16 @@
         <v>2002</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -763,16 +790,16 @@
         <v>2003</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -780,16 +807,16 @@
         <v>2004</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -797,16 +824,16 @@
         <v>2005</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -814,16 +841,16 @@
         <v>2006</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -831,16 +858,16 @@
         <v>2007</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -848,16 +875,16 @@
         <v>2008</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -865,16 +892,16 @@
         <v>2009</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -897,19 +924,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -917,16 +944,16 @@
         <v>3001</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -934,16 +961,16 @@
         <v>3002</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -951,16 +978,16 @@
         <v>3003</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -968,16 +995,16 @@
         <v>3004</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -985,16 +1012,16 @@
         <v>3005</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1002,16 +1029,16 @@
         <v>3006</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1019,16 +1046,16 @@
         <v>3007</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1036,16 +1063,16 @@
         <v>3008</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1053,16 +1080,16 @@
         <v>3009</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
